--- a/student_import_demo.xlsx
+++ b/student_import_demo.xlsx
@@ -452,26 +452,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="112" customHeight="1">
+    <row r="1" ht="126" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>填写说明：
 * 必填列。
 登录账号(学号)：租户内唯一，已存在则跳过。
 密码：长度至少 8 位，且需同时包含字母和数字。
-班级：须与系统中已存在的组织节点名称完全一致。
-专业代码：填写系统中已存在的专业代码，匹配则关联，不匹配则忽略。
+班级(组织节点路径)：填写系统中已存在的组织节点完整路径，可自动匹配末级节点。
+  示例：某某职业技术学院-信息工程学院-软件技术2401班，或使用 /、-&gt; 等分隔符。
+  若班级名称唯一，也可只写班级名称（如：软件技术2401班）。
 状态：在籍 / 休学 / 退学 / 毕业 / 结业，默认为在籍。</t>
         </is>
       </c>
@@ -494,15 +494,10 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>班级(组织节点名称) *</t>
+          <t>班级(组织节点路径) *</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>专业代码</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -526,15 +521,10 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>软件技术2401班</t>
+          <t>某某职业技术学院-信息工程学院-软件技术2401班</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SE202</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -558,15 +548,10 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>软件技术2401班</t>
+          <t>某某职业技术学院-信息工程学院-软件技术2401班</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SE202</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -590,15 +575,10 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>软件技术2402班</t>
+          <t>某某职业技术学院-信息工程学院-软件技术2402班</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SE202</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -622,15 +602,10 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>人工智能2401班</t>
+          <t>某某职业技术学院-信息工程学院-人工智能2401班</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>AI303</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -654,15 +629,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>新能源汽车2401班</t>
+          <t>某某职业技术学院-汽车工程学院-新能源汽车2401班</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>NE401</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -686,15 +656,10 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>新能源汽车2402班</t>
+          <t>某某职业技术学院-汽车工程学院-新能源汽车2402班</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>NE401</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -718,15 +683,10 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>工业机器人2401班</t>
+          <t>某某职业技术学院-智能制造学院-工业机器人2401班</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ROB601</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -750,15 +710,10 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>大数据与会计2401班</t>
+          <t>某某职业技术学院-经济管理学院-大数据与会计2401班</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>AC901</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -782,15 +737,10 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>软件技术2401班</t>
+          <t>某某职业技术学院-信息工程学院-软件技术2401班</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>SE202</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -814,15 +764,10 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>人工智能2401班</t>
+          <t>某某职业技术学院-信息工程学院-人工智能2401班</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>AI303</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>在籍</t>
         </is>
@@ -830,7 +775,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
